--- a/server/excel/release/personal-space.xlsx
+++ b/server/excel/release/personal-space.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="头像" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="头像框" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="称号" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="皮肤" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="冒险形象" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="皮肤穿戴管理" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="皮肤技能特效替换" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="皮肤状态特效" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="条件说明Sheet" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Sheet称号数据备份" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sheet1" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Sheet头像备份" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Sheet冒险形象备份" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="头像" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="头像框" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="称号" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皮肤" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冒险形象" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皮肤穿戴管理" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皮肤技能特效替换" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皮肤状态特效" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件说明Sheet" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet称号数据备份" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet头像备份" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet冒险形象备份" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">1160</t>
   </si>
   <si>
-    <t xml:space="preserve">Chu Điên</t>
+    <t xml:space="preserve">Bartolomeo</t>
   </si>
   <si>
     <t xml:space="preserve">1150</t>
